--- a/myprojects/RVNL/RVNL_Ratio_Analysis.xlsx
+++ b/myprojects/RVNL/RVNL_Ratio_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\RVNL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831CABC0-E1E1-491F-87B7-A1C12AEE4F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C794895F-BAAB-4264-A4BC-F55465607F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Leverage" sheetId="5" r:id="rId5"/>
     <sheet name="Efficiency" sheetId="6" r:id="rId6"/>
     <sheet name="Trend Analysis" sheetId="7" r:id="rId7"/>
-    <sheet name="FPA Insights" sheetId="8" r:id="rId8"/>
+    <sheet name="Insights" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1089,9 +1089,6 @@
     <t>FP&amp;A LEVEL INSIGHTS AND REAL-WORLD CONTEXT - RAIL VIKAS NIGAM LIMITED</t>
   </si>
   <si>
-    <t>Here is what the numbers mean for the business | Analyst commentary for FY2022-23 to FY2024-25</t>
-  </si>
-  <si>
     <t>Area</t>
   </si>
   <si>
@@ -1267,6 +1264,9 @@
   </si>
   <si>
     <t>Model made by Anjani Kumar Mishra</t>
+  </si>
+  <si>
+    <t>Here is what the numbers mean for the business</t>
   </si>
 </sst>
 </file>
@@ -1792,6 +1792,30 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1805,46 +1829,32 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1855,21 +1865,11 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2141,242 +2141,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
     </row>
     <row r="3" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="79" t="s">
+      <c r="B7" s="79"/>
+      <c r="C7" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="79" t="s">
+      <c r="B9" s="79"/>
+      <c r="C9" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
     </row>
     <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="80" t="s">
+      <c r="B12" s="74"/>
+      <c r="C12" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
     </row>
     <row r="13" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="80" t="s">
+      <c r="B13" s="74"/>
+      <c r="C13" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
     </row>
     <row r="14" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="80" t="s">
+      <c r="B14" s="74"/>
+      <c r="C14" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
     </row>
     <row r="15" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="80" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
     </row>
     <row r="16" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="80" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
     </row>
     <row r="17" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="80" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
     </row>
     <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="80" t="s">
+      <c r="B18" s="74"/>
+      <c r="C18" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="80"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -2385,30 +2385,30 @@
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="84"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C22" s="85" t="s">
+        <v>405</v>
+      </c>
+      <c r="C22" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -2417,14 +2417,14 @@
       <c r="B23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="85" t="s">
+      <c r="C23" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -2433,14 +2433,14 @@
       <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="85" t="s">
+      <c r="C24" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -2449,14 +2449,14 @@
       <c r="B25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -2465,14 +2465,14 @@
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="85" t="s">
+      <c r="C26" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
@@ -2481,14 +2481,14 @@
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="85" t="s">
+      <c r="C27" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -2497,14 +2497,14 @@
       <c r="B28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="85" t="s">
+      <c r="C28" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -2513,14 +2513,14 @@
       <c r="B29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="85" t="s">
+      <c r="C29" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
@@ -2534,6 +2534,39 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C22:H22"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="C23:H23"/>
@@ -2541,39 +2574,6 @@
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:H4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2591,22 +2591,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -2621,10 +2621,10 @@
       <c r="D3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="87"/>
+      <c r="F3" s="92"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="88" t="s">
@@ -2649,10 +2649,10 @@
       <c r="D5" s="7">
         <v>19869.349999999999</v>
       </c>
-      <c r="E5" s="89" t="s">
+      <c r="E5" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="89"/>
+      <c r="F5" s="86"/>
     </row>
     <row r="6" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
@@ -2667,10 +2667,10 @@
       <c r="D6" s="9">
         <v>1018.89</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="87"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
@@ -2685,10 +2685,10 @@
       <c r="D7" s="11">
         <v>20888.240000000002</v>
       </c>
-      <c r="E7" s="91" t="s">
+      <c r="E7" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="91"/>
+      <c r="F7" s="89"/>
     </row>
     <row r="8" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -2703,10 +2703,10 @@
       <c r="D8" s="9">
         <v>18385.2</v>
       </c>
-      <c r="E8" s="90" t="s">
+      <c r="E8" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="90"/>
+      <c r="F8" s="87"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -2721,8 +2721,8 @@
       <c r="D9" s="7">
         <v>182.98</v>
       </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
     </row>
     <row r="10" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -2737,10 +2737,10 @@
       <c r="D10" s="9">
         <v>539.51</v>
       </c>
-      <c r="E10" s="90" t="s">
+      <c r="E10" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="90"/>
+      <c r="F10" s="87"/>
     </row>
     <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
@@ -2755,8 +2755,8 @@
       <c r="D11" s="7">
         <v>30.6</v>
       </c>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
@@ -2771,8 +2771,8 @@
       <c r="D12" s="9">
         <v>199.78</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
@@ -2787,10 +2787,10 @@
       <c r="D13" s="11">
         <v>19338.07</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="91"/>
+      <c r="F13" s="89"/>
     </row>
     <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -2805,10 +2805,10 @@
       <c r="D14" s="9">
         <v>2089.6799999999998</v>
       </c>
-      <c r="E14" s="90" t="s">
+      <c r="E14" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="90"/>
+      <c r="F14" s="87"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -2823,10 +2823,10 @@
       <c r="D15" s="7">
         <v>2120.2800000000002</v>
       </c>
-      <c r="E15" s="89" t="s">
+      <c r="E15" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="89"/>
+      <c r="F15" s="86"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
@@ -2841,8 +2841,8 @@
       <c r="D16" s="9">
         <v>1550.17</v>
       </c>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
     </row>
     <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -2857,8 +2857,8 @@
       <c r="D17" s="7">
         <v>361.55</v>
       </c>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
@@ -2873,10 +2873,10 @@
       <c r="D18" s="11">
         <v>1188.6199999999999</v>
       </c>
-      <c r="E18" s="91" t="s">
+      <c r="E18" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="91"/>
+      <c r="F18" s="89"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="88" t="s">
@@ -2901,10 +2901,10 @@
       <c r="D21" s="11">
         <v>8012.02</v>
       </c>
-      <c r="E21" s="91" t="s">
+      <c r="E21" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="91"/>
+      <c r="F21" s="89"/>
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
@@ -2919,10 +2919,10 @@
       <c r="D22" s="9">
         <v>537.21</v>
       </c>
-      <c r="E22" s="90" t="s">
+      <c r="E22" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="90"/>
+      <c r="F22" s="87"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
@@ -2937,10 +2937,10 @@
       <c r="D23" s="7">
         <v>1764.13</v>
       </c>
-      <c r="E23" s="89" t="s">
+      <c r="E23" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="89"/>
+      <c r="F23" s="86"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
@@ -2955,10 +2955,10 @@
       <c r="D24" s="9">
         <v>3992.85</v>
       </c>
-      <c r="E24" s="90" t="s">
+      <c r="E24" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="90"/>
+      <c r="F24" s="87"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
@@ -2973,10 +2973,10 @@
       <c r="D25" s="11">
         <v>11472.5</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="91"/>
+      <c r="F25" s="89"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
@@ -2991,10 +2991,10 @@
       <c r="D26" s="9">
         <v>1489.51</v>
       </c>
-      <c r="E26" s="90" t="s">
+      <c r="E26" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="90"/>
+      <c r="F26" s="87"/>
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
@@ -3009,10 +3009,10 @@
       <c r="D27" s="7">
         <v>3044.8</v>
       </c>
-      <c r="E27" s="89" t="s">
+      <c r="E27" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="F27" s="89"/>
+      <c r="F27" s="86"/>
     </row>
     <row r="28" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
@@ -3027,10 +3027,10 @@
       <c r="D28" s="9">
         <v>718.44</v>
       </c>
-      <c r="E28" s="90" t="s">
+      <c r="E28" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="90"/>
+      <c r="F28" s="87"/>
     </row>
     <row r="29" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
@@ -3045,10 +3045,10 @@
       <c r="D29" s="7">
         <v>499.51</v>
       </c>
-      <c r="E29" s="89" t="s">
+      <c r="E29" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="89"/>
+      <c r="F29" s="86"/>
     </row>
     <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
@@ -3063,8 +3063,8 @@
       <c r="D30" s="9">
         <v>2584.1799999999998</v>
       </c>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
     </row>
     <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
@@ -3079,10 +3079,10 @@
       <c r="D31" s="7">
         <v>3075.13</v>
       </c>
-      <c r="E31" s="89" t="s">
+      <c r="E31" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="F31" s="89"/>
+      <c r="F31" s="86"/>
     </row>
     <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
@@ -3097,10 +3097,10 @@
       <c r="D32" s="11">
         <v>19484.52</v>
       </c>
-      <c r="E32" s="91" t="s">
+      <c r="E32" s="89" t="s">
         <v>108</v>
       </c>
-      <c r="F32" s="91"/>
+      <c r="F32" s="89"/>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
@@ -3115,10 +3115,10 @@
       <c r="D34" s="11">
         <v>8623.7199999999993</v>
       </c>
-      <c r="E34" s="91" t="s">
+      <c r="E34" s="89" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="91"/>
+      <c r="F34" s="89"/>
     </row>
     <row r="35" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
@@ -3133,10 +3133,10 @@
       <c r="D35" s="7">
         <v>2085.02</v>
       </c>
-      <c r="E35" s="89" t="s">
+      <c r="E35" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="89"/>
+      <c r="F35" s="86"/>
     </row>
     <row r="36" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -3151,10 +3151,10 @@
       <c r="D36" s="9">
         <v>6538.7</v>
       </c>
-      <c r="E36" s="90" t="s">
+      <c r="E36" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="90"/>
+      <c r="F36" s="87"/>
     </row>
     <row r="37" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
@@ -3169,10 +3169,10 @@
       <c r="D37" s="11">
         <v>5252.5</v>
       </c>
-      <c r="E37" s="91" t="s">
+      <c r="E37" s="89" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="91"/>
+      <c r="F37" s="89"/>
     </row>
     <row r="38" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
@@ -3187,10 +3187,10 @@
       <c r="D38" s="9">
         <v>4889.51</v>
       </c>
-      <c r="E38" s="90" t="s">
+      <c r="E38" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="F38" s="90"/>
+      <c r="F38" s="87"/>
     </row>
     <row r="39" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
@@ -3205,10 +3205,10 @@
       <c r="D39" s="11">
         <v>5608.3</v>
       </c>
-      <c r="E39" s="91" t="s">
+      <c r="E39" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="F39" s="91"/>
+      <c r="F39" s="89"/>
     </row>
     <row r="40" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
@@ -3223,10 +3223,10 @@
       <c r="D40" s="9">
         <v>499.51</v>
       </c>
-      <c r="E40" s="90" t="s">
+      <c r="E40" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="F40" s="90"/>
+      <c r="F40" s="87"/>
     </row>
     <row r="41" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
@@ -3241,10 +3241,10 @@
       <c r="D41" s="7">
         <v>344.87</v>
       </c>
-      <c r="E41" s="89" t="s">
+      <c r="E41" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="89"/>
+      <c r="F41" s="86"/>
     </row>
     <row r="42" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -3259,8 +3259,8 @@
       <c r="D42" s="9">
         <v>2228.35</v>
       </c>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
+      <c r="E42" s="87"/>
+      <c r="F42" s="87"/>
     </row>
     <row r="43" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
@@ -3275,10 +3275,10 @@
       <c r="D43" s="7">
         <v>2416.9299999999998</v>
       </c>
-      <c r="E43" s="89" t="s">
+      <c r="E43" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="89"/>
+      <c r="F43" s="86"/>
     </row>
     <row r="44" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
@@ -3293,10 +3293,10 @@
       <c r="D44" s="11">
         <v>19484.52</v>
       </c>
-      <c r="E44" s="91" t="s">
+      <c r="E44" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="91"/>
+      <c r="F44" s="89"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="88" t="s">
@@ -3321,10 +3321,10 @@
       <c r="D47" s="7">
         <v>1919.9</v>
       </c>
-      <c r="E47" s="89" t="s">
+      <c r="E47" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="89"/>
+      <c r="F47" s="86"/>
     </row>
     <row r="48" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
@@ -3339,10 +3339,10 @@
       <c r="D48" s="9">
         <v>1581.62</v>
       </c>
-      <c r="E48" s="90" t="s">
+      <c r="E48" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="F48" s="90"/>
+      <c r="F48" s="87"/>
     </row>
     <row r="49" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
@@ -3357,10 +3357,10 @@
       <c r="D49" s="7">
         <v>-1484.17</v>
       </c>
-      <c r="E49" s="89" t="s">
+      <c r="E49" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="F49" s="89"/>
+      <c r="F49" s="86"/>
     </row>
     <row r="50" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
@@ -3375,10 +3375,10 @@
       <c r="D50" s="9">
         <v>2017.31</v>
       </c>
-      <c r="E50" s="90" t="s">
+      <c r="E50" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="F50" s="90"/>
+      <c r="F50" s="87"/>
     </row>
     <row r="51" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
@@ -3393,10 +3393,10 @@
       <c r="D51" s="7">
         <v>3044.8</v>
       </c>
-      <c r="E51" s="89" t="s">
+      <c r="E51" s="86" t="s">
         <v>140</v>
       </c>
-      <c r="F51" s="89"/>
+      <c r="F51" s="86"/>
     </row>
     <row r="52" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
@@ -3411,10 +3411,10 @@
       <c r="D52" s="9">
         <v>462.66</v>
       </c>
-      <c r="E52" s="90" t="s">
+      <c r="E52" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="F52" s="90"/>
+      <c r="F52" s="87"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="88" t="s">
@@ -3442,10 +3442,10 @@
         <f>D38+D40</f>
         <v>5389.02</v>
       </c>
-      <c r="E55" s="90" t="s">
+      <c r="E55" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="F55" s="90"/>
+      <c r="F55" s="87"/>
     </row>
     <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
@@ -3463,10 +3463,10 @@
         <f>D55-D27</f>
         <v>2344.2200000000003</v>
       </c>
-      <c r="E56" s="89" t="s">
+      <c r="E56" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="F56" s="89"/>
+      <c r="F56" s="86"/>
     </row>
     <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
@@ -3484,10 +3484,10 @@
         <f>D16+D10</f>
         <v>2089.6800000000003</v>
       </c>
-      <c r="E57" s="90" t="s">
+      <c r="E57" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="F57" s="90"/>
+      <c r="F57" s="87"/>
     </row>
     <row r="58" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
@@ -3505,10 +3505,10 @@
         <f>D57+D11</f>
         <v>2120.2800000000002</v>
       </c>
-      <c r="E58" s="89" t="s">
+      <c r="E58" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="F58" s="89"/>
+      <c r="F58" s="86"/>
     </row>
     <row r="59" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
@@ -3526,10 +3526,10 @@
         <f>D32-D39</f>
         <v>13876.220000000001</v>
       </c>
-      <c r="E59" s="90" t="s">
+      <c r="E59" s="87" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="90"/>
+      <c r="F59" s="87"/>
     </row>
     <row r="60" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
@@ -3547,10 +3547,10 @@
         <f>D5-D8</f>
         <v>1484.1499999999978</v>
       </c>
-      <c r="E60" s="89" t="s">
+      <c r="E60" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="F60" s="89"/>
+      <c r="F60" s="86"/>
     </row>
     <row r="61" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
@@ -3568,10 +3568,10 @@
         <f>(C32+D32)/2</f>
         <v>19109.025000000001</v>
       </c>
-      <c r="E61" s="90" t="s">
+      <c r="E61" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="F61" s="90"/>
+      <c r="F61" s="87"/>
     </row>
     <row r="62" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
@@ -3589,14 +3589,14 @@
         <f>(C34+D34)/2</f>
         <v>8245.5</v>
       </c>
-      <c r="E62" s="89" t="s">
+      <c r="E62" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="F62" s="89"/>
+      <c r="F62" s="86"/>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3606,6 +3606,56 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="E62:F62"/>
@@ -3614,56 +3664,6 @@
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3700,34 +3700,34 @@
       <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="93"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="72" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B4" s="72"/>
       <c r="C4" s="72"/>
@@ -3740,18 +3740,18 @@
       <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
@@ -3769,14 +3769,14 @@
         <f>'Raw Data'!D5</f>
         <v>19869.349999999999</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
@@ -3794,14 +3794,14 @@
         <f>'Raw Data'!D6</f>
         <v>1018.89</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
@@ -3819,14 +3819,14 @@
         <f>'Raw Data'!D7</f>
         <v>20888.240000000002</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
@@ -3844,14 +3844,14 @@
         <f>'Raw Data'!D8</f>
         <v>18385.2</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="18" t="s">
@@ -3869,14 +3869,14 @@
         <f>'Raw Data'!D9</f>
         <v>182.98</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
@@ -3894,14 +3894,14 @@
         <f>'Raw Data'!D10</f>
         <v>539.51</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
@@ -3919,14 +3919,14 @@
         <f>'Raw Data'!D11</f>
         <v>30.6</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
@@ -3944,14 +3944,14 @@
         <f>'Raw Data'!D12</f>
         <v>199.78</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
@@ -3969,14 +3969,14 @@
         <f>'Raw Data'!D13</f>
         <v>19338.07</v>
       </c>
-      <c r="E14" s="95" t="s">
+      <c r="E14" s="93" t="s">
         <v>170</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
@@ -3994,14 +3994,14 @@
         <f>'Raw Data'!D57</f>
         <v>2089.6800000000003</v>
       </c>
-      <c r="E15" s="96" t="s">
+      <c r="E15" s="94" t="s">
         <v>172</v>
       </c>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="18" t="s">
@@ -4019,14 +4019,14 @@
         <f>'Raw Data'!D58</f>
         <v>2120.2800000000002</v>
       </c>
-      <c r="E16" s="95" t="s">
+      <c r="E16" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -4044,14 +4044,14 @@
         <f>'Raw Data'!D16</f>
         <v>1550.17</v>
       </c>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
@@ -4069,14 +4069,14 @@
         <f>'Raw Data'!D17</f>
         <v>361.55</v>
       </c>
-      <c r="E18" s="95" t="s">
+      <c r="E18" s="93" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="95"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
@@ -4094,14 +4094,14 @@
         <f>'Raw Data'!D18</f>
         <v>1188.6199999999999</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="94" t="s">
         <v>176</v>
       </c>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="18" t="s">
@@ -4119,14 +4119,14 @@
         <f>'Raw Data'!D34</f>
         <v>8623.7199999999993</v>
       </c>
-      <c r="E20" s="95" t="s">
+      <c r="E20" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
@@ -4144,14 +4144,14 @@
         <f>'Raw Data'!D32</f>
         <v>19484.52</v>
       </c>
-      <c r="E21" s="96" t="s">
+      <c r="E21" s="94" t="s">
         <v>178</v>
       </c>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
@@ -4169,14 +4169,14 @@
         <f>'Raw Data'!D59</f>
         <v>13876.220000000001</v>
       </c>
-      <c r="E22" s="95" t="s">
+      <c r="E22" s="93" t="s">
         <v>179</v>
       </c>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="95"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
@@ -4194,14 +4194,14 @@
         <f>'Raw Data'!D62</f>
         <v>8245.5</v>
       </c>
-      <c r="E23" s="96" t="s">
+      <c r="E23" s="94" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="18" t="s">
@@ -4219,39 +4219,39 @@
         <f>'Raw Data'!D61</f>
         <v>19109.025000000001</v>
       </c>
-      <c r="E24" s="95" t="s">
+      <c r="E24" s="93" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="97" t="s">
+      <c r="A25" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="B25" s="97">
+      <c r="B25" s="95">
         <f>'Raw Data'!B35</f>
         <v>2085.02</v>
       </c>
-      <c r="C25" s="97">
+      <c r="C25" s="95">
         <f>'Raw Data'!C35</f>
         <v>2085.02</v>
       </c>
-      <c r="D25" s="97">
+      <c r="D25" s="95">
         <f>'Raw Data'!D35</f>
         <v>2085.02</v>
       </c>
-      <c r="E25" s="97" t="s">
+      <c r="E25" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="18" t="s">
@@ -4269,14 +4269,14 @@
         <f>'Raw Data'!D60</f>
         <v>1484.1499999999978</v>
       </c>
-      <c r="E26" s="95" t="s">
+      <c r="E26" s="93" t="s">
         <v>184</v>
       </c>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="95"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="35"/>
@@ -4627,7 +4627,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B40" s="39"/>
       <c r="C40" s="39"/>
@@ -4641,32 +4641,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="E15:J15"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="E20:J20"/>
     <mergeCell ref="E26:J26"/>
     <mergeCell ref="E21:J21"/>
     <mergeCell ref="E22:J22"/>
     <mergeCell ref="E23:J23"/>
     <mergeCell ref="E24:J24"/>
     <mergeCell ref="A25:J25"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="E18:J18"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="E15:J15"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4702,32 +4702,32 @@
       <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
     </row>
     <row r="3" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="s">
@@ -4744,18 +4744,18 @@
       <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
@@ -4773,14 +4773,14 @@
         <f>'Raw Data'!D25</f>
         <v>11472.5</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
@@ -4798,14 +4798,14 @@
         <f>'Raw Data'!D39</f>
         <v>5608.3</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="94" t="s">
         <v>228</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
@@ -4823,14 +4823,14 @@
         <f>'Raw Data'!D31</f>
         <v>3075.13</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
@@ -4848,14 +4848,14 @@
         <f>'Raw Data'!D27</f>
         <v>3044.8</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
@@ -4873,26 +4873,26 @@
         <f>'Raw Data'!D47</f>
         <v>1919.9</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="98"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="32"/>
@@ -5151,7 +5151,7 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
@@ -5165,17 +5165,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="E6:J6"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E10:J10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5212,32 +5212,32 @@
       <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
     </row>
     <row r="3" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="s">
@@ -5254,18 +5254,18 @@
       <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
@@ -5283,14 +5283,14 @@
         <f>'Raw Data'!D55</f>
         <v>5389.02</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
@@ -5308,14 +5308,14 @@
         <f>'Raw Data'!D56</f>
         <v>2344.2200000000003</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="94" t="s">
         <v>261</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
@@ -5333,14 +5333,14 @@
         <f>'Raw Data'!D34</f>
         <v>8623.7199999999993</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
@@ -5358,14 +5358,14 @@
         <f>'Raw Data'!D32</f>
         <v>19484.52</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="94" t="s">
         <v>178</v>
       </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
@@ -5383,14 +5383,14 @@
         <f>'Raw Data'!D57</f>
         <v>2089.6800000000003</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
@@ -5408,14 +5408,14 @@
         <f>'Raw Data'!D10</f>
         <v>539.51</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
@@ -5433,14 +5433,14 @@
         <f>'Raw Data'!D58</f>
         <v>2120.2800000000002</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
@@ -5458,26 +5458,26 @@
         <f>'Raw Data'!D38</f>
         <v>4889.51</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="94" t="s">
         <v>263</v>
       </c>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
@@ -5773,7 +5773,7 @@
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B25" s="39"/>
       <c r="C25" s="39"/>
@@ -5787,6 +5787,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E12:J12"/>
     <mergeCell ref="E13:J13"/>
@@ -5796,11 +5801,6 @@
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E10:J10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5838,32 +5838,32 @@
       <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
     </row>
     <row r="3" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="s">
@@ -5880,18 +5880,18 @@
       <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
@@ -5909,14 +5909,14 @@
         <f>'Raw Data'!D5</f>
         <v>19869.349999999999</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
@@ -5934,14 +5934,14 @@
         <f>'Raw Data'!D61</f>
         <v>19109.025000000001</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
@@ -5959,14 +5959,14 @@
         <f>'Raw Data'!D26</f>
         <v>1489.51</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="93" t="s">
         <v>291</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
@@ -5984,14 +5984,14 @@
         <f>'Raw Data'!D41</f>
         <v>344.87</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="94" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
@@ -6009,14 +6009,14 @@
         <f>'Raw Data'!D8</f>
         <v>18385.2</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
@@ -6034,14 +6034,14 @@
         <f>'Raw Data'!D25</f>
         <v>11472.5</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="94" t="s">
         <v>227</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
@@ -6059,14 +6059,14 @@
         <f>'Raw Data'!D39</f>
         <v>5608.3</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="93" t="s">
         <v>228</v>
       </c>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
@@ -6084,26 +6084,26 @@
         <f>'Raw Data'!D34</f>
         <v>8623.7199999999993</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B24" s="39"/>
       <c r="C24" s="39"/>
@@ -6376,6 +6376,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E12:J12"/>
     <mergeCell ref="E13:J13"/>
@@ -6385,11 +6390,6 @@
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E10:J10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6458,12 +6458,12 @@
       <c r="D5" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="98" t="s">
         <v>322</v>
       </c>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
     </row>
     <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
@@ -6481,12 +6481,12 @@
         <f>'Raw Data'!D5</f>
         <v>19869.349999999999</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
@@ -6504,12 +6504,12 @@
         <f>'Raw Data'!D6</f>
         <v>1018.89</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
@@ -6527,12 +6527,12 @@
         <f>'Raw Data'!D7</f>
         <v>20888.240000000002</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
     </row>
     <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
@@ -6550,24 +6550,24 @@
         <f>'Raw Data'!D8</f>
         <v>18385.2</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
     </row>
     <row r="10" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
     </row>
     <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
@@ -6585,12 +6585,12 @@
         <f>'Raw Data'!D58</f>
         <v>2120.2800000000002</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
     </row>
     <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
@@ -6608,12 +6608,12 @@
         <f>'Raw Data'!D32</f>
         <v>19484.52</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="93" t="s">
         <v>178</v>
       </c>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
     </row>
     <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
@@ -6631,12 +6631,12 @@
         <f>'Raw Data'!D34</f>
         <v>8623.7199999999993</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
     </row>
     <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
@@ -6654,12 +6654,12 @@
         <f>'Raw Data'!D55</f>
         <v>5389.02</v>
       </c>
-      <c r="E14" s="95" t="s">
+      <c r="E14" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
     </row>
     <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
@@ -6677,24 +6677,24 @@
         <f>'Raw Data'!D27</f>
         <v>3044.8</v>
       </c>
-      <c r="E15" s="96" t="s">
+      <c r="E15" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
     </row>
     <row r="16" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="100" t="s">
         <v>290</v>
       </c>
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
     </row>
     <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
@@ -6712,58 +6712,58 @@
         <f>'Raw Data'!D47</f>
         <v>1919.9</v>
       </c>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
     </row>
     <row r="18" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="99">
+      <c r="B18" s="100">
         <f>'Raw Data'!B25</f>
         <v>9000.36</v>
       </c>
-      <c r="C18" s="99">
+      <c r="C18" s="100">
         <f>'Raw Data'!C25</f>
         <v>9666.6</v>
       </c>
-      <c r="D18" s="99">
+      <c r="D18" s="100">
         <f>'Raw Data'!D25</f>
         <v>11472.5</v>
       </c>
-      <c r="E18" s="99" t="s">
+      <c r="E18" s="100" t="s">
         <v>227</v>
       </c>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
     </row>
     <row r="19" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="95" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="97">
+      <c r="B19" s="95">
         <f>'Raw Data'!B39</f>
         <v>4447.3500000000004</v>
       </c>
-      <c r="C19" s="97">
+      <c r="C19" s="95">
         <f>'Raw Data'!C39</f>
         <v>4583.5</v>
       </c>
-      <c r="D19" s="97">
+      <c r="D19" s="95">
         <f>'Raw Data'!D39</f>
         <v>5608.3</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="95" t="s">
         <v>228</v>
       </c>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
     </row>
     <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
@@ -6781,12 +6781,12 @@
         <f>'Raw Data'!D57</f>
         <v>2089.6800000000003</v>
       </c>
-      <c r="E20" s="95" t="s">
+      <c r="E20" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
     </row>
     <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
@@ -6804,12 +6804,12 @@
         <f>'Raw Data'!D10</f>
         <v>539.51</v>
       </c>
-      <c r="E21" s="96" t="s">
+      <c r="E21" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
     </row>
     <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35"/>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="45" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A45" s="39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B45" s="39"/>
       <c r="C45" s="39"/>
@@ -7415,26 +7415,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7447,7 +7447,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.6640625" customWidth="1"/>
     <col min="3" max="3" width="55.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="B2" s="71"/>
       <c r="C2" s="71"/>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="72" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B3" s="72"/>
       <c r="C3" s="72"/>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -7501,49 +7501,49 @@
     </row>
     <row r="5" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="55" t="s">
+        <v>350</v>
+      </c>
+      <c r="B5" s="56" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="57" t="s">
         <v>352</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="D5" s="58" t="s">
         <v>353</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="E5" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="F5" s="60" t="s">
         <v>355</v>
-      </c>
-      <c r="F5" s="60" t="s">
-        <v>356</v>
       </c>
       <c r="G5" s="32"/>
     </row>
     <row r="6" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="61" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="62" t="s">
         <v>357</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="C6" s="63" t="s">
         <v>358</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>359</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="E6" s="65" t="s">
         <v>360</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="F6" s="66" t="s">
         <v>361</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>362</v>
       </c>
       <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="68" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="9" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
@@ -7574,70 +7574,70 @@
     </row>
     <row r="10" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="B10" s="62" t="s">
         <v>365</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="C10" s="63" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="D10" s="64" t="s">
         <v>367</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="E10" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="E10" s="65" t="s">
+      <c r="F10" s="66" t="s">
         <v>369</v>
-      </c>
-      <c r="F10" s="66" t="s">
-        <v>370</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="55" t="s">
+        <v>370</v>
+      </c>
+      <c r="B11" s="56" t="s">
         <v>371</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="C11" s="57" t="s">
         <v>372</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="D11" s="58" t="s">
         <v>373</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="E11" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="F11" s="60" t="s">
         <v>375</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>376</v>
       </c>
       <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="C12" s="63" t="s">
         <v>378</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="D12" s="64" t="s">
         <v>379</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="E12" s="65" t="s">
         <v>380</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="F12" s="66" t="s">
         <v>381</v>
-      </c>
-      <c r="F12" s="66" t="s">
-        <v>382</v>
       </c>
       <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="68" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B13" s="68"/>
       <c r="C13" s="68"/>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="15" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -7668,64 +7668,64 @@
     </row>
     <row r="16" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="62" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="C16" s="63" t="s">
         <v>386</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="D16" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="E16" s="65" t="s">
         <v>388</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="F16" s="66" t="s">
         <v>389</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>390</v>
       </c>
       <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="56" t="s">
         <v>391</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="57" t="s">
         <v>392</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="D17" s="58" t="s">
         <v>393</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="E17" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="E17" s="59" t="s">
+      <c r="F17" s="60" t="s">
         <v>395</v>
-      </c>
-      <c r="F17" s="60" t="s">
-        <v>396</v>
       </c>
       <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:7" ht="81.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="B18" s="62" t="s">
         <v>397</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="C18" s="63" t="s">
         <v>398</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="D18" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="D18" s="64" t="s">
+      <c r="E18" s="65" t="s">
         <v>400</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="F18" s="66" t="s">
         <v>401</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>402</v>
       </c>
       <c r="G18" s="32"/>
     </row>
